--- a/DATA_BASE_HARINAS_v3.xlsx
+++ b/DATA_BASE_HARINAS_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d36a139ff44747e4/Desktop/Tesis/CODIGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6CA5A92-8C31-4500-B4A5-AEB404F1AD32}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A5E3603-9E29-477E-AF85-B3C0ACDA556C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIMITES MARRAQUETA" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="262">
   <si>
     <t>EFECTOS INCREMENTALES DE ADITIVOS EN LA MEZCLA</t>
   </si>
@@ -806,9 +806,6 @@
   </si>
   <si>
     <t>PRECIOS DE INSUMOS Y PARÁMETROS ECONÓMICOS — DSS MARRAQUETA</t>
-  </si>
-  <si>
-    <t>Actualizar los valores de la columna "Valor_CLP" cuando cambien los precios. El DSS carga esta hoja automáticamente — no requiere modificar el código Python. Fecha de última actualización: registrar en columna "Fecha_Referencia".</t>
   </si>
   <si>
     <t>SECCIÓN 1: INSUMOS PANADEROS (costo por kg de harina usado en receta)</t>
@@ -1211,7 +1208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1316,17 +1313,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1335,6 +1323,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1352,6 +1346,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1949,7 +1947,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="38" t="s">
         <v>78</v>
       </c>
       <c r="B14" s="39"/>
@@ -3044,7 +3042,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -3054,7 +3052,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -3091,7 +3089,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
@@ -3339,7 +3337,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="42" t="s">
         <v>162</v>
       </c>
       <c r="B1" s="39"/>
@@ -3347,7 +3345,7 @@
       <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="40" t="s">
         <v>163</v>
       </c>
       <c r="B2" s="39"/>
@@ -3536,7 +3534,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>191</v>
       </c>
       <c r="B1" s="39"/>
@@ -3547,19 +3545,11 @@
       <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="37"/>
+    </row>
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="43" t="s">
         <v>192</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-    </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="38" t="s">
-        <v>193</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -3570,22 +3560,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="C5" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="D5" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="E5" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="F5" s="30" t="s">
         <v>198</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>199</v>
       </c>
       <c r="G5" s="30" t="s">
         <v>7</v>
@@ -3593,122 +3583,122 @@
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>200</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>201</v>
       </c>
       <c r="C6" s="32">
         <v>2500</v>
       </c>
       <c r="D6" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="F6" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="G6" s="34" t="s">
         <v>204</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>206</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>207</v>
       </c>
       <c r="C7" s="32">
         <v>150</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E7" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>208</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>210</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>211</v>
       </c>
       <c r="C8" s="32">
         <v>3000</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E8" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>212</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>214</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>215</v>
       </c>
       <c r="C9" s="32">
         <v>5</v>
       </c>
       <c r="D9" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="F9" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="34" t="s">
         <v>217</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="31" t="s">
         <v>219</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>220</v>
       </c>
       <c r="C10" s="32">
         <v>1200</v>
       </c>
       <c r="D10" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G10" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>208</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="34" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="43" t="s">
         <v>222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="38" t="s">
-        <v>223</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -3719,22 +3709,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="D14" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="E14" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="F14" s="30" t="s">
         <v>198</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>199</v>
       </c>
       <c r="G14" s="30" t="s">
         <v>7</v>
@@ -3742,122 +3732,122 @@
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="35" t="s">
         <v>224</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>225</v>
       </c>
       <c r="C15" s="32">
         <v>180</v>
       </c>
       <c r="D15" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="F15" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15" s="34" t="s">
         <v>227</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>229</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>230</v>
       </c>
       <c r="C16" s="32">
         <v>45</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="34" t="s">
         <v>231</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="35" t="s">
         <v>233</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>234</v>
       </c>
       <c r="C17" s="32">
         <v>8</v>
       </c>
       <c r="D17" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="F17" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G17" s="34" t="s">
         <v>236</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>238</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>239</v>
       </c>
       <c r="C18" s="32">
         <v>25</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E18" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" s="34" t="s">
         <v>240</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="B19" s="35" t="s">
         <v>242</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>243</v>
       </c>
       <c r="C19" s="32">
         <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G19" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="F19" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G19" s="34" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="43" t="s">
         <v>245</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="38" t="s">
-        <v>246</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
@@ -3868,22 +3858,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="C23" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="D23" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="E23" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="F23" s="30" t="s">
         <v>198</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>199</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>7</v>
@@ -3891,33 +3881,33 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="36" t="s">
         <v>247</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>248</v>
       </c>
       <c r="C24" s="32">
         <v>250</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E24" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G24" s="34" t="s">
         <v>249</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="B25" s="36" t="s">
         <v>251</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>252</v>
       </c>
       <c r="C25" s="32">
         <v>35</v>
@@ -3926,21 +3916,21 @@
         <v>171</v>
       </c>
       <c r="E25" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G25" s="34" t="s">
         <v>253</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="36" t="s">
         <v>255</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>256</v>
       </c>
       <c r="C26" s="32">
         <v>0</v>
@@ -3949,21 +3939,21 @@
         <v>171</v>
       </c>
       <c r="E26" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G26" s="34" t="s">
         <v>257</v>
-      </c>
-      <c r="F26" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="36" t="s">
         <v>259</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>260</v>
       </c>
       <c r="C27" s="32">
         <v>3</v>
@@ -3972,25 +3962,24 @@
         <v>171</v>
       </c>
       <c r="E27" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="34" t="s">
         <v>261</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DATA_BASE_HARINAS_v3.xlsx
+++ b/DATA_BASE_HARINAS_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d36a139ff44747e4/Desktop/Tesis/CODIGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A5E3603-9E29-477E-AF85-B3C0ACDA556C}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1487C1A4-9A7D-42C0-98A4-6ED5BEE55717}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIMITES MARRAQUETA" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="262">
   <si>
     <t>EFECTOS INCREMENTALES DE ADITIVOS EN LA MEZCLA</t>
   </si>
@@ -286,9 +286,6 @@
     <t>extension</t>
   </si>
   <si>
-    <t>Reduce extensibilidad L. Efecto negativo a &gt;2%.</t>
-  </si>
-  <si>
     <t>fibra</t>
   </si>
   <si>
@@ -322,18 +319,12 @@
     <t>Tebben 2019 (Cereal Chemistry, Wiley)</t>
   </si>
   <si>
-    <t>0.2% XG eleva absorción de 59% a 60.8% → ~0.4% por cada 0.1% de XG.</t>
-  </si>
-  <si>
     <t>Tebben 2019 / Linlaud et al. 2009</t>
   </si>
   <si>
     <t>XG aumenta resistencia a extensión (P). Efecto pronunciado a 0.1-0.3%.</t>
   </si>
   <si>
-    <t>Brennan &amp; Tudorica 2007 (ScienceDirect)</t>
-  </si>
-  <si>
     <t>XG reduce extensibilidad L. Exceso (&gt;0.5%) hace masa muy tenaz.</t>
   </si>
   <si>
@@ -1016,6 +1007,15 @@
   </si>
   <si>
     <t>Pérdidas por proceso sobre la producción estimada. Rango típico: 2-5%. Validar con datos reales del establecimiento.</t>
+  </si>
+  <si>
+    <t>Farbo et al. 2020 (Food Hydrocolloids)</t>
+  </si>
+  <si>
+    <t>Efecto positivo a dosis ≤1%. Farbo (2020) reporta aumento de extensibilidad con 1% psyllium en masa panaria. Efecto dosis-dependiente: se revierte a dosis altas o con hidratación insuficiente.</t>
+  </si>
+  <si>
+    <t>Farbo et al. 2020</t>
   </si>
 </sst>
 </file>
@@ -1313,14 +1313,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1346,10 +1346,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1682,30 +1678,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -1717,55 +1713,55 @@
         <v>20</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>15</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>24</v>
@@ -1774,18 +1770,18 @@
         <v>30</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>85</v>
@@ -1794,18 +1790,18 @@
         <v>100</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>58</v>
@@ -1820,15 +1816,15 @@
         <v>9</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1837,18 +1833,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1857,18 +1853,18 @@
         <v>15</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B10">
         <v>200</v>
@@ -1877,18 +1873,18 @@
         <v>260</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B11">
         <v>65</v>
@@ -1900,15 +1896,15 @@
         <v>13</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12">
         <v>60</v>
@@ -1920,15 +1916,15 @@
         <v>17</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B13">
         <v>0.7</v>
@@ -1937,18 +1933,18 @@
         <v>1.6</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="38" t="s">
-        <v>78</v>
+      <c r="A14" s="41" t="s">
+        <v>75</v>
       </c>
       <c r="B14" s="39"/>
       <c r="C14" s="39"/>
@@ -1959,7 +1955,7 @@
     </row>
     <row r="15" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B15" s="14">
         <v>0.5</v>
@@ -1971,18 +1967,18 @@
         <v>8</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B16" s="14">
         <v>0.5</v>
@@ -1994,18 +1990,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" s="14">
         <v>1.7</v>
@@ -2015,18 +2011,18 @@
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B18" s="14">
         <v>2</v>
@@ -2036,13 +2032,13 @@
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2089,111 +2085,111 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B2" s="18">
         <v>613.09</v>
@@ -2202,16 +2198,16 @@
         <v>493.67094017094013</v>
       </c>
       <c r="D2" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>126</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="H2" s="17">
         <v>2</v>
@@ -2226,10 +2222,10 @@
         <v>260</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N2" s="17">
         <v>80</v>
@@ -2250,25 +2246,25 @@
         <v>65</v>
       </c>
       <c r="T2" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="X2" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y2" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="U2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="V2" s="17" t="s">
+      <c r="Z2" s="17" t="s">
         <v>133</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="X2" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y2" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z2" s="17" t="s">
-        <v>136</v>
       </c>
       <c r="AA2" s="17">
         <v>15</v>
@@ -2286,18 +2282,18 @@
         <v>9</v>
       </c>
       <c r="AF2" s="17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AG2" s="18">
         <v>0.63</v>
       </c>
       <c r="AH2" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B3" s="18">
         <v>720.52</v>
@@ -2312,10 +2308,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H3" s="20">
         <v>2</v>
@@ -2357,19 +2353,19 @@
         <v>0</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="V3" s="17">
         <v>0</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="X3" s="17">
         <v>0</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Z3" s="17">
         <v>11</v>
@@ -2393,15 +2389,15 @@
         <v>1</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B4" s="18">
         <v>1059.1199999999999</v>
@@ -2416,16 +2412,16 @@
         <v>8</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H4" s="17">
         <v>1</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J4" s="17">
         <v>0</v>
@@ -2458,22 +2454,22 @@
         <v>72</v>
       </c>
       <c r="T4" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="X4" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="U4" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="V4" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="W4" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="X4" s="17" t="s">
-        <v>149</v>
-      </c>
       <c r="Y4" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Z4" s="17">
         <v>10</v>
@@ -2494,18 +2490,18 @@
         <v>15</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AH4" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B5" s="18">
         <v>1323.4</v>
@@ -2523,7 +2519,7 @@
         <v>4.5</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H5" s="17">
         <v>10</v>
@@ -2562,22 +2558,22 @@
         <v>85</v>
       </c>
       <c r="T5" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="V5" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="W5" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="U5" s="17" t="s">
+      <c r="X5" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y5" s="17" t="s">
         <v>154</v>
-      </c>
-      <c r="V5" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="W5" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="X5" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y5" s="17" t="s">
-        <v>157</v>
       </c>
       <c r="Z5" s="17">
         <v>10</v>
@@ -2598,18 +2594,18 @@
         <v>6</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AG5" s="20">
         <v>2.8</v>
       </c>
       <c r="AH5" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B6" s="18">
         <v>1547.6</v>
@@ -2666,22 +2662,22 @@
         <v>90</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="V6" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="W6" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="X6" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y6" s="17" t="s">
         <v>156</v>
-      </c>
-      <c r="Y6" s="17" t="s">
-        <v>159</v>
       </c>
       <c r="Z6" s="17">
         <v>10</v>
@@ -2702,13 +2698,13 @@
         <v>6</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG6" s="20">
         <v>2.5</v>
       </c>
       <c r="AH6" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.35">
@@ -2812,12 +2808,12 @@
         <v>2.5</v>
       </c>
       <c r="AH7" s="22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="18">
         <v>15000</v>
@@ -2916,12 +2912,12 @@
         <v>8</v>
       </c>
       <c r="AH8" s="22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B9" s="23">
         <v>3000</v>
@@ -3020,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="23" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3042,7 +3038,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -3052,7 +3048,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -3129,16 +3125,16 @@
         <v>17</v>
       </c>
       <c r="C6" s="4">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3146,19 +3142,19 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4">
         <v>65</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3166,17 +3162,17 @@
         <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3184,22 +3180,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
@@ -3211,15 +3207,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>30</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>13</v>
@@ -3231,84 +3225,84 @@
         <v>14</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>33</v>
+        <v>261</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6">
         <v>0</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="6">
         <v>0</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3338,15 +3332,15 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="42" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
       <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
-        <v>163</v>
+      <c r="A2" s="38" t="s">
+        <v>160</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -3354,13 +3348,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
@@ -3369,10 +3363,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>5</v>
@@ -3383,132 +3377,132 @@
     </row>
     <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="25">
+        <v>0</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="G4" s="27" t="s">
         <v>170</v>
-      </c>
-      <c r="C4" s="25">
-        <v>0</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>173</v>
       </c>
       <c r="H4" s="28">
         <v>210</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C5" s="25">
         <v>1.75</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H5" s="28">
         <v>82.2</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C6" s="25">
         <v>2</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H6" s="28">
         <v>10</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" s="25">
         <v>0.4</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H7" s="28">
         <v>13.5</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="G8" s="27" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H8" s="28">
         <v>60</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3535,7 +3529,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -3549,7 +3543,7 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -3560,22 +3554,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="E5" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="F5" s="30" t="s">
         <v>195</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>198</v>
       </c>
       <c r="G5" s="30" t="s">
         <v>7</v>
@@ -3583,122 +3577,122 @@
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="31" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C6" s="32">
         <v>2500</v>
       </c>
       <c r="D6" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="G6" s="34" t="s">
         <v>201</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C7" s="32">
         <v>150</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="31" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C8" s="32">
         <v>3000</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C9" s="32">
         <v>5</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C10" s="32">
         <v>1200</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="43" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -3709,22 +3703,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="E14" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="F14" s="30" t="s">
         <v>195</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>198</v>
       </c>
       <c r="G14" s="30" t="s">
         <v>7</v>
@@ -3732,122 +3726,122 @@
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="35" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C15" s="32">
         <v>180</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C16" s="32">
         <v>45</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="35" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C17" s="32">
         <v>8</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C18" s="32">
         <v>25</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C19" s="32">
         <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="43" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
@@ -3858,22 +3852,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="E23" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="F23" s="30" t="s">
         <v>195</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>198</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>7</v>
@@ -3881,94 +3875,94 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="36" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C24" s="32">
         <v>250</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C25" s="32">
         <v>35</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="C26" s="32">
+        <v>0</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="G26" s="34" t="s">
         <v>254</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="C26" s="32">
-        <v>0</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="F26" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="36" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C27" s="32">
         <v>3</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">

--- a/DATA_BASE_HARINAS_v3.xlsx
+++ b/DATA_BASE_HARINAS_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d36a139ff44747e4/Desktop/Tesis/CODIGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1487C1A4-9A7D-42C0-98A4-6ED5BEE55717}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A5B22A8-FC48-4BC4-AD52-43D1B0049B0D}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIMITES MARRAQUETA" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="261">
   <si>
     <t>EFECTOS INCREMENTALES DE ADITIVOS EN LA MEZCLA</t>
   </si>
@@ -265,12 +265,6 @@
     <t>% abs</t>
   </si>
   <si>
-    <t>Aldughpassi et al. 2020 (Int. J. Food Sci.)</t>
-  </si>
-  <si>
-    <t>Cada 1% psyllium → +4% absorción farinográfica. VERIFICADO.</t>
-  </si>
-  <si>
     <t>tenacidad</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
     <t>fibra</t>
   </si>
   <si>
-    <t>% /100g</t>
-  </si>
-  <si>
     <t>Composición psyllium husk (FDA/USDA)</t>
   </si>
   <si>
@@ -319,15 +310,9 @@
     <t>Tebben 2019 (Cereal Chemistry, Wiley)</t>
   </si>
   <si>
-    <t>Tebben 2019 / Linlaud et al. 2009</t>
-  </si>
-  <si>
     <t>XG aumenta resistencia a extensión (P). Efecto pronunciado a 0.1-0.3%.</t>
   </si>
   <si>
-    <t>XG reduce extensibilidad L. Exceso (&gt;0.5%) hace masa muy tenaz.</t>
-  </si>
-  <si>
     <t>Aditivo funcional, no aporta fibra significativa.</t>
   </si>
   <si>
@@ -1016,6 +1001,18 @@
   </si>
   <si>
     <t>Farbo et al. 2020</t>
+  </si>
+  <si>
+    <t>4% psyllium eleva absorción de 56,6% a 81,8% (+25,2 puntos). Bajo supuesto de linealidad: 6,3 puntos por cada 1%</t>
+  </si>
+  <si>
+    <t>Mironeasa &amp; Codină</t>
+  </si>
+  <si>
+    <t>Efecto positivo a dosis baja. Farbo (2020) reporta aumento de extensibilidad con 1% de XG en masa panaria. Efecto dosis-dependiente: se revierte por agotamiento de agua a dosis altas</t>
+  </si>
+  <si>
+    <t>Linlaud et al. 2009</t>
   </si>
 </sst>
 </file>
@@ -1678,30 +1675,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -1713,55 +1710,55 @@
         <v>20</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>15</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>24</v>
@@ -1770,18 +1767,18 @@
         <v>30</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B6">
         <v>85</v>
@@ -1790,18 +1787,18 @@
         <v>100</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>58</v>
@@ -1816,15 +1813,15 @@
         <v>9</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1833,18 +1830,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1853,18 +1850,18 @@
         <v>15</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B10">
         <v>200</v>
@@ -1873,18 +1870,18 @@
         <v>260</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B11">
         <v>65</v>
@@ -1893,18 +1890,18 @@
         <v>110</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B12">
         <v>60</v>
@@ -1913,18 +1910,18 @@
         <v>110</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B13">
         <v>0.7</v>
@@ -1933,18 +1930,18 @@
         <v>1.6</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B14" s="39"/>
       <c r="C14" s="39"/>
@@ -1955,7 +1952,7 @@
     </row>
     <row r="15" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B15" s="14">
         <v>0.5</v>
@@ -1967,18 +1964,18 @@
         <v>8</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B16" s="14">
         <v>0.5</v>
@@ -1990,18 +1987,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B17" s="14">
         <v>1.7</v>
@@ -2011,18 +2008,18 @@
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B18" s="14">
         <v>2</v>
@@ -2032,13 +2029,13 @@
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2085,111 +2082,111 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B2" s="18">
         <v>613.09</v>
@@ -2198,16 +2195,16 @@
         <v>493.67094017094013</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H2" s="17">
         <v>2</v>
@@ -2222,10 +2219,10 @@
         <v>260</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="N2" s="17">
         <v>80</v>
@@ -2246,25 +2243,25 @@
         <v>65</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="V2" s="17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="W2" s="17" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="X2" s="17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Y2" s="17" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="Z2" s="17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="AA2" s="17">
         <v>15</v>
@@ -2282,18 +2279,18 @@
         <v>9</v>
       </c>
       <c r="AF2" s="17" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AG2" s="18">
         <v>0.63</v>
       </c>
       <c r="AH2" s="19" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B3" s="18">
         <v>720.52</v>
@@ -2308,10 +2305,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H3" s="20">
         <v>2</v>
@@ -2353,19 +2350,19 @@
         <v>0</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="V3" s="17">
         <v>0</v>
       </c>
       <c r="W3" s="17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="X3" s="17">
         <v>0</v>
       </c>
       <c r="Y3" s="17" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Z3" s="17">
         <v>11</v>
@@ -2389,15 +2386,15 @@
         <v>1</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AH3" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B4" s="18">
         <v>1059.1199999999999</v>
@@ -2412,16 +2409,16 @@
         <v>8</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H4" s="17">
         <v>1</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J4" s="17">
         <v>0</v>
@@ -2454,22 +2451,22 @@
         <v>72</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="Y4" s="17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="Z4" s="17">
         <v>10</v>
@@ -2490,18 +2487,18 @@
         <v>15</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AH4" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B5" s="18">
         <v>1323.4</v>
@@ -2519,7 +2516,7 @@
         <v>4.5</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H5" s="17">
         <v>10</v>
@@ -2558,22 +2555,22 @@
         <v>85</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="V5" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="X5" s="17" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Y5" s="17" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="Z5" s="17">
         <v>10</v>
@@ -2594,18 +2591,18 @@
         <v>6</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="AG5" s="20">
         <v>2.8</v>
       </c>
       <c r="AH5" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B6" s="18">
         <v>1547.6</v>
@@ -2662,22 +2659,22 @@
         <v>90</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="V6" s="17" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="W6" s="17" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="X6" s="17" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="Y6" s="17" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="Z6" s="17">
         <v>10</v>
@@ -2698,13 +2695,13 @@
         <v>6</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AG6" s="20">
         <v>2.5</v>
       </c>
       <c r="AH6" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.35">
@@ -2808,12 +2805,12 @@
         <v>2.5</v>
       </c>
       <c r="AH7" s="22" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B8" s="18">
         <v>15000</v>
@@ -2912,12 +2909,12 @@
         <v>8</v>
       </c>
       <c r="AH8" s="22" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B9" s="23">
         <v>3000</v>
@@ -3016,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="23" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3091,10 +3088,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>12</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3102,19 +3099,19 @@
         <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4">
         <v>1.5</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3122,19 +3119,19 @@
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3142,19 +3139,19 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="4">
-        <v>65</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3162,17 +3159,17 @@
         <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3180,22 +3177,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
@@ -3207,102 +3204,102 @@
         <v>10</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6">
         <v>1.8</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6">
         <v>1.5</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6">
         <v>0</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C15" s="6">
         <v>0</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3332,7 +3329,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="42" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -3340,7 +3337,7 @@
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -3348,13 +3345,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>5</v>
@@ -3363,10 +3360,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>5</v>
@@ -3377,132 +3374,132 @@
     </row>
     <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C4" s="25">
         <v>0</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H4" s="28">
         <v>210</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C5" s="25">
         <v>1.75</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H5" s="28">
         <v>82.2</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C6" s="25">
         <v>2</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H6" s="28">
         <v>10</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C7" s="25">
         <v>0.4</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H7" s="28">
         <v>13.5</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="G8" s="27" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H8" s="28">
         <v>60</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3529,7 +3526,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -3543,7 +3540,7 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -3554,22 +3551,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="30" t="s">
         <v>190</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>195</v>
       </c>
       <c r="G5" s="30" t="s">
         <v>7</v>
@@ -3577,122 +3574,122 @@
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="31" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C6" s="32">
         <v>2500</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C7" s="32">
         <v>150</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F7" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>200</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="31" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C8" s="32">
         <v>3000</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C9" s="32">
         <v>5</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C10" s="32">
         <v>1200</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="43" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -3703,22 +3700,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F14" s="30" t="s">
         <v>190</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>195</v>
       </c>
       <c r="G14" s="30" t="s">
         <v>7</v>
@@ -3726,122 +3723,122 @@
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="35" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C15" s="32">
         <v>180</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C16" s="32">
         <v>45</v>
       </c>
       <c r="D16" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="E16" s="34" t="s">
-        <v>227</v>
-      </c>
       <c r="F16" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="35" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C17" s="32">
         <v>8</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C18" s="32">
         <v>25</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C19" s="32">
         <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="43" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
@@ -3852,22 +3849,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>190</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>195</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>7</v>
@@ -3875,94 +3872,94 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="36" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C24" s="32">
         <v>250</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C25" s="32">
         <v>35</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="36" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C26" s="32">
         <v>0</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="36" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C27" s="32">
         <v>3</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">

--- a/DATA_BASE_HARINAS_v3.xlsx
+++ b/DATA_BASE_HARINAS_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d36a139ff44747e4/Desktop/Tesis/CODIGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A5B22A8-FC48-4BC4-AD52-43D1B0049B0D}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047CEFC1-4097-4117-8907-762F680AF645}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIMITES MARRAQUETA" sheetId="1" r:id="rId1"/>
@@ -886,9 +886,6 @@
     <t>CLP/kg pan</t>
   </si>
   <si>
-    <t>Estimado: sueldo panadero $700.000/mes, 200kg pan/día, 22 días</t>
-  </si>
-  <si>
     <t>Calcular según: sueldo_mensual / (kg_pan_dia * dias_mes). Ajustar según tamaño de panadería y número de trabajadores.</t>
   </si>
   <si>
@@ -949,12 +946,6 @@
     <t>precio_venta_marraqueta</t>
   </si>
   <si>
-    <t>Precio venta sugerido marraqueta (210g)</t>
-  </si>
-  <si>
-    <t>Precio promedio panadería barrio Santiago, jun-2026</t>
-  </si>
-  <si>
     <t>Referencia: $200-350/unidad según sector y calidad. Permite calcular margen bruto en el DSS.</t>
   </si>
   <si>
@@ -1013,6 +1004,15 @@
   </si>
   <si>
     <t>Linlaud et al. 2009</t>
+  </si>
+  <si>
+    <t>Precio venta sugerido marraqueta (105g)</t>
+  </si>
+  <si>
+    <t>Precio promedio ODEPA 2025: $2.219/kg (≈$233 por unidad de 105 g)</t>
+  </si>
+  <si>
+    <t>IMM $529.000/mes (Ley 21.751) × 1,25 leyes sociales</t>
   </si>
 </sst>
 </file>
@@ -3088,10 +3088,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3128,10 +3128,10 @@
         <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3222,7 +3222,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>26</v>
@@ -3242,10 +3242,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3735,21 +3735,21 @@
         <v>217</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="F15" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>220</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>221</v>
       </c>
       <c r="C16" s="32">
         <v>45</v>
@@ -3758,44 +3758,44 @@
         <v>217</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F16" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="35" t="s">
         <v>224</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>225</v>
       </c>
       <c r="C17" s="32">
         <v>8</v>
       </c>
       <c r="D17" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="34" t="s">
         <v>226</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>227</v>
       </c>
       <c r="F17" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>229</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>230</v>
       </c>
       <c r="C18" s="32">
         <v>25</v>
@@ -3804,21 +3804,21 @@
         <v>217</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F18" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="35" t="s">
         <v>233</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>234</v>
       </c>
       <c r="C19" s="32">
         <v>60</v>
@@ -3827,18 +3827,18 @@
         <v>217</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F19" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="43" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
@@ -3872,33 +3872,33 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="C24" s="32">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="F24" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C25" s="32">
         <v>35</v>
@@ -3907,21 +3907,21 @@
         <v>163</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F25" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="36" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C26" s="32">
         <v>0</v>
@@ -3930,21 +3930,21 @@
         <v>163</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F26" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C27" s="32">
         <v>3</v>
@@ -3953,13 +3953,13 @@
         <v>163</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F27" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">

--- a/DATA_BASE_HARINAS_v3.xlsx
+++ b/DATA_BASE_HARINAS_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d36a139ff44747e4/Desktop/Tesis/CODIGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047CEFC1-4097-4117-8907-762F680AF645}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_6944C8CA768BB38188428622408D02CEA391E6B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62E9D0E-2F16-416F-B5C0-F8FEECDB4577}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LIMITES MARRAQUETA" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="257">
   <si>
     <t>EFECTOS INCREMENTALES DE ADITIVOS EN LA MEZCLA</t>
   </si>
@@ -860,18 +860,6 @@
   </si>
   <si>
     <t>Tarifa industrial ~$4-6/lt. Incluir si aplica medidor independiente. Si es agua de pozo o tarifa diferente, actualizar.</t>
-  </si>
-  <si>
-    <t>aceite_vegetal</t>
-  </si>
-  <si>
-    <t>Aceite vegetal (pincelado superficial)</t>
-  </si>
-  <si>
-    <t>CLP/lt</t>
-  </si>
-  <si>
-    <t>Opcional. Receta Lefersa indica pincelar bollos antes de fermentación. Consumo estimado: ~5ml por marraqueta.</t>
   </si>
   <si>
     <t>SECCIÓN 2: COSTOS OPERACIONALES (no incluidos en precio de harinas)</t>
@@ -1310,22 +1298,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3035,7 +3023,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -3045,7 +3033,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -3088,10 +3076,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3128,10 +3116,10 @@
         <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3222,7 +3210,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>26</v>
@@ -3242,10 +3230,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3328,7 +3316,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>154</v>
       </c>
       <c r="B1" s="39"/>
@@ -3336,7 +3324,7 @@
       <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="42" t="s">
         <v>155</v>
       </c>
       <c r="B2" s="39"/>
@@ -3513,7 +3501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3525,7 +3513,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>183</v>
       </c>
       <c r="B1" s="39"/>
@@ -3539,7 +3527,7 @@
       <c r="A2" s="37"/>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="38" t="s">
         <v>184</v>
       </c>
       <c r="B4" s="39"/>
@@ -3664,61 +3652,61 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="32">
-        <v>1200</v>
-      </c>
-      <c r="D10" s="33" t="s">
+      <c r="B14" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="33" t="s">
+      <c r="C14" s="32">
+        <v>180</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="43" t="s">
+      <c r="G14" s="34" t="s">
         <v>214</v>
-      </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3729,13 +3717,13 @@
         <v>216</v>
       </c>
       <c r="C15" s="32">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="D15" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="34" t="s">
         <v>217</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>260</v>
       </c>
       <c r="F15" s="33" t="s">
         <v>195</v>
@@ -3752,33 +3740,33 @@
         <v>220</v>
       </c>
       <c r="C16" s="32">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F16" s="33" t="s">
         <v>195</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" s="32">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E17" s="34" t="s">
         <v>226</v>
@@ -3798,10 +3786,10 @@
         <v>229</v>
       </c>
       <c r="C18" s="32">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E18" s="34" t="s">
         <v>230</v>
@@ -3813,78 +3801,78 @@
         <v>231</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="35" t="s">
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="32">
-        <v>60</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E19" s="34" t="s">
+      <c r="B23" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" s="32">
+        <v>233</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="G23" s="34" t="s">
         <v>234</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="F23" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="32">
+        <v>35</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="34" t="s">
         <v>237</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="C24" s="32">
-        <v>233</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>259</v>
       </c>
       <c r="F24" s="33" t="s">
         <v>195</v>
@@ -3901,7 +3889,7 @@
         <v>240</v>
       </c>
       <c r="C25" s="32">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D25" s="33" t="s">
         <v>163</v>
@@ -3924,7 +3912,7 @@
         <v>244</v>
       </c>
       <c r="C26" s="32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>163</v>
@@ -3939,39 +3927,17 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="32">
-        <v>3</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="37"/>
+    <row r="28" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>